--- a/daily_ethnicity_mix.xlsx
+++ b/daily_ethnicity_mix.xlsx
@@ -12286,7 +12286,7 @@
         </is>
       </c>
       <c r="B297" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C297" t="n">
         <v>30</v>
@@ -12310,13 +12310,13 @@
         <v>18</v>
       </c>
       <c r="J297" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K297" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L297" t="n">
-        <v>77.2</v>
+        <v>76.90000000000001</v>
       </c>
     </row>
     <row r="298">
@@ -24114,7 +24114,7 @@
         </is>
       </c>
       <c r="C290" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D290" t="n">
         <v>14</v>
@@ -24138,7 +24138,7 @@
         <v>11</v>
       </c>
       <c r="K290" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="291">

--- a/daily_ethnicity_mix.xlsx
+++ b/daily_ethnicity_mix.xlsx
@@ -12766,19 +12766,19 @@
         </is>
       </c>
       <c r="B309" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C309" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D309" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E309" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F309" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G309" t="n">
         <v>0</v>
@@ -12787,16 +12787,16 @@
         <v>0</v>
       </c>
       <c r="I309" t="n">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="J309" t="n">
-        <v>12</v>
+        <v>91</v>
       </c>
       <c r="K309" t="n">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="L309" t="n">
-        <v>58.3</v>
+        <v>46.2</v>
       </c>
     </row>
   </sheetData>
@@ -12810,7 +12810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K669"/>
+  <dimension ref="A1:K670"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24582,19 +24582,19 @@
         </is>
       </c>
       <c r="C302" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D302" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E302" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F302" t="n">
         <v>0</v>
       </c>
       <c r="G302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H302" t="n">
         <v>0</v>
@@ -24603,10 +24603,10 @@
         <v>0</v>
       </c>
       <c r="J302" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="K302" t="n">
-        <v>3</v>
+        <v>46</v>
       </c>
     </row>
     <row r="303">
@@ -28287,16 +28287,16 @@
         </is>
       </c>
       <c r="C397" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D397" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E397" t="n">
         <v>1</v>
       </c>
       <c r="F397" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G397" t="n">
         <v>0</v>
@@ -28308,10 +28308,10 @@
         <v>0</v>
       </c>
       <c r="J397" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="K397" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
     </row>
     <row r="398">
@@ -34098,10 +34098,10 @@
         </is>
       </c>
       <c r="C546" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D546" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E546" t="n">
         <v>0</v>
@@ -34119,10 +34119,10 @@
         <v>0</v>
       </c>
       <c r="J546" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K546" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="547">
@@ -36897,19 +36897,19 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>Ashwagandha</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="C618" t="n">
         <v>0</v>
       </c>
       <c r="D618" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E618" t="n">
         <v>0</v>
@@ -36918,7 +36918,7 @@
         <v>0</v>
       </c>
       <c r="G618" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H618" t="n">
         <v>0</v>
@@ -36927,16 +36927,16 @@
         <v>0</v>
       </c>
       <c r="J618" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K618" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
@@ -36945,7 +36945,7 @@
         </is>
       </c>
       <c r="C619" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D619" t="n">
         <v>0</v>
@@ -36957,7 +36957,7 @@
         <v>0</v>
       </c>
       <c r="G619" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H619" t="n">
         <v>0</v>
@@ -36975,7 +36975,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
@@ -37005,16 +37005,16 @@
         <v>0</v>
       </c>
       <c r="J620" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K620" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
@@ -37023,7 +37023,7 @@
         </is>
       </c>
       <c r="C621" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D621" t="n">
         <v>0</v>
@@ -37032,7 +37032,7 @@
         <v>0</v>
       </c>
       <c r="F621" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G621" t="n">
         <v>0</v>
@@ -37053,7 +37053,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
@@ -37062,7 +37062,7 @@
         </is>
       </c>
       <c r="C622" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D622" t="n">
         <v>0</v>
@@ -37071,7 +37071,7 @@
         <v>0</v>
       </c>
       <c r="F622" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G622" t="n">
         <v>0</v>
@@ -37086,13 +37086,13 @@
         <v>0</v>
       </c>
       <c r="K622" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
@@ -37101,10 +37101,10 @@
         </is>
       </c>
       <c r="C623" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D623" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E623" t="n">
         <v>0</v>
@@ -37122,16 +37122,16 @@
         <v>0</v>
       </c>
       <c r="J623" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K623" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
@@ -37140,13 +37140,13 @@
         </is>
       </c>
       <c r="C624" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D624" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E624" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F624" t="n">
         <v>0</v>
@@ -37161,16 +37161,16 @@
         <v>0</v>
       </c>
       <c r="J624" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K624" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
@@ -37179,13 +37179,13 @@
         </is>
       </c>
       <c r="C625" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D625" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E625" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F625" t="n">
         <v>0</v>
@@ -37197,19 +37197,19 @@
         <v>0</v>
       </c>
       <c r="I625" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J625" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K625" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
@@ -37218,7 +37218,7 @@
         </is>
       </c>
       <c r="C626" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D626" t="n">
         <v>0</v>
@@ -37236,19 +37236,19 @@
         <v>0</v>
       </c>
       <c r="I626" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J626" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K626" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
@@ -37257,7 +37257,7 @@
         </is>
       </c>
       <c r="C627" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D627" t="n">
         <v>0</v>
@@ -37278,16 +37278,16 @@
         <v>0</v>
       </c>
       <c r="J627" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K627" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
@@ -37317,16 +37317,16 @@
         <v>0</v>
       </c>
       <c r="J628" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K628" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
@@ -37335,7 +37335,7 @@
         </is>
       </c>
       <c r="C629" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D629" t="n">
         <v>0</v>
@@ -37356,7 +37356,7 @@
         <v>0</v>
       </c>
       <c r="J629" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K629" t="n">
         <v>2</v>
@@ -37365,7 +37365,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
@@ -37374,13 +37374,13 @@
         </is>
       </c>
       <c r="C630" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D630" t="n">
         <v>0</v>
       </c>
       <c r="E630" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F630" t="n">
         <v>0</v>
@@ -37395,16 +37395,16 @@
         <v>0</v>
       </c>
       <c r="J630" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K630" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
@@ -37413,13 +37413,13 @@
         </is>
       </c>
       <c r="C631" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D631" t="n">
         <v>0</v>
       </c>
       <c r="E631" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F631" t="n">
         <v>0</v>
@@ -37434,16 +37434,16 @@
         <v>0</v>
       </c>
       <c r="J631" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K631" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
@@ -37455,7 +37455,7 @@
         <v>0</v>
       </c>
       <c r="D632" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E632" t="n">
         <v>0</v>
@@ -37473,7 +37473,7 @@
         <v>0</v>
       </c>
       <c r="J632" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K632" t="n">
         <v>1</v>
@@ -37482,7 +37482,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
@@ -37521,7 +37521,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
@@ -37539,7 +37539,7 @@
         <v>0</v>
       </c>
       <c r="F634" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G634" t="n">
         <v>0</v>
@@ -37554,13 +37554,13 @@
         <v>0</v>
       </c>
       <c r="K634" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
@@ -37569,16 +37569,16 @@
         </is>
       </c>
       <c r="C635" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D635" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E635" t="n">
         <v>0</v>
       </c>
       <c r="F635" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G635" t="n">
         <v>0</v>
@@ -37590,7 +37590,7 @@
         <v>0</v>
       </c>
       <c r="J635" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K635" t="n">
         <v>2</v>
@@ -37599,7 +37599,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
@@ -37638,7 +37638,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
@@ -37677,7 +37677,7 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
@@ -37686,7 +37686,7 @@
         </is>
       </c>
       <c r="C638" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D638" t="n">
         <v>0</v>
@@ -37710,13 +37710,13 @@
         <v>1</v>
       </c>
       <c r="K638" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
@@ -37755,7 +37755,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
@@ -37794,7 +37794,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
@@ -37803,7 +37803,7 @@
         </is>
       </c>
       <c r="C641" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D641" t="n">
         <v>0</v>
@@ -37824,16 +37824,16 @@
         <v>0</v>
       </c>
       <c r="J641" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K641" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
@@ -37842,7 +37842,7 @@
         </is>
       </c>
       <c r="C642" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D642" t="n">
         <v>0</v>
@@ -37863,16 +37863,16 @@
         <v>0</v>
       </c>
       <c r="J642" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K642" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
@@ -37881,7 +37881,7 @@
         </is>
       </c>
       <c r="C643" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D643" t="n">
         <v>0</v>
@@ -37902,16 +37902,16 @@
         <v>0</v>
       </c>
       <c r="J643" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K643" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
@@ -37920,7 +37920,7 @@
         </is>
       </c>
       <c r="C644" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D644" t="n">
         <v>0</v>
@@ -37944,13 +37944,13 @@
         <v>1</v>
       </c>
       <c r="K644" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
@@ -37959,7 +37959,7 @@
         </is>
       </c>
       <c r="C645" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D645" t="n">
         <v>0</v>
@@ -37983,13 +37983,13 @@
         <v>1</v>
       </c>
       <c r="K645" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
@@ -38019,16 +38019,16 @@
         <v>0</v>
       </c>
       <c r="J646" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K646" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
@@ -38037,7 +38037,7 @@
         </is>
       </c>
       <c r="C647" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D647" t="n">
         <v>0</v>
@@ -38061,13 +38061,13 @@
         <v>0</v>
       </c>
       <c r="K647" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
@@ -38076,7 +38076,7 @@
         </is>
       </c>
       <c r="C648" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D648" t="n">
         <v>0</v>
@@ -38100,13 +38100,13 @@
         <v>0</v>
       </c>
       <c r="K648" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
@@ -38145,7 +38145,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
@@ -38154,7 +38154,7 @@
         </is>
       </c>
       <c r="C650" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D650" t="n">
         <v>0</v>
@@ -38163,7 +38163,7 @@
         <v>0</v>
       </c>
       <c r="F650" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G650" t="n">
         <v>0</v>
@@ -38184,7 +38184,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
@@ -38193,7 +38193,7 @@
         </is>
       </c>
       <c r="C651" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D651" t="n">
         <v>0</v>
@@ -38202,7 +38202,7 @@
         <v>0</v>
       </c>
       <c r="F651" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G651" t="n">
         <v>0</v>
@@ -38214,16 +38214,16 @@
         <v>0</v>
       </c>
       <c r="J651" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K651" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
@@ -38232,7 +38232,7 @@
         </is>
       </c>
       <c r="C652" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D652" t="n">
         <v>0</v>
@@ -38253,7 +38253,7 @@
         <v>0</v>
       </c>
       <c r="J652" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K652" t="n">
         <v>2</v>
@@ -38262,7 +38262,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
@@ -38271,7 +38271,7 @@
         </is>
       </c>
       <c r="C653" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D653" t="n">
         <v>0</v>
@@ -38292,16 +38292,16 @@
         <v>0</v>
       </c>
       <c r="J653" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K653" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
@@ -38340,7 +38340,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
@@ -38349,7 +38349,7 @@
         </is>
       </c>
       <c r="C655" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D655" t="n">
         <v>0</v>
@@ -38370,7 +38370,7 @@
         <v>0</v>
       </c>
       <c r="J655" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K655" t="n">
         <v>1</v>
@@ -38379,16 +38379,16 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>GUTSHIFT</t>
+          <t>Ashwagandha</t>
         </is>
       </c>
       <c r="C656" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D656" t="n">
         <v>0</v>
@@ -38409,16 +38409,16 @@
         <v>0</v>
       </c>
       <c r="J656" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K656" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
@@ -38427,10 +38427,10 @@
         </is>
       </c>
       <c r="C657" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D657" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E657" t="n">
         <v>0</v>
@@ -38439,7 +38439,7 @@
         <v>0</v>
       </c>
       <c r="G657" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H657" t="n">
         <v>0</v>
@@ -38448,16 +38448,16 @@
         <v>0</v>
       </c>
       <c r="J657" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K657" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
@@ -38469,16 +38469,16 @@
         <v>0</v>
       </c>
       <c r="D658" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E658" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F658" t="n">
         <v>0</v>
       </c>
       <c r="G658" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H658" t="n">
         <v>0</v>
@@ -38490,13 +38490,13 @@
         <v>0</v>
       </c>
       <c r="K658" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
@@ -38505,13 +38505,13 @@
         </is>
       </c>
       <c r="C659" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D659" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E659" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F659" t="n">
         <v>0</v>
@@ -38529,13 +38529,13 @@
         <v>0</v>
       </c>
       <c r="K659" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
@@ -38544,10 +38544,10 @@
         </is>
       </c>
       <c r="C660" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D660" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E660" t="n">
         <v>0</v>
@@ -38556,7 +38556,7 @@
         <v>0</v>
       </c>
       <c r="G660" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H660" t="n">
         <v>0</v>
@@ -38568,13 +38568,13 @@
         <v>0</v>
       </c>
       <c r="K660" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
@@ -38583,7 +38583,7 @@
         </is>
       </c>
       <c r="C661" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D661" t="n">
         <v>0</v>
@@ -38595,7 +38595,7 @@
         <v>0</v>
       </c>
       <c r="G661" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H661" t="n">
         <v>0</v>
@@ -38613,7 +38613,7 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
@@ -38622,16 +38622,16 @@
         </is>
       </c>
       <c r="C662" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D662" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E662" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F662" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G662" t="n">
         <v>0</v>
@@ -38646,13 +38646,13 @@
         <v>0</v>
       </c>
       <c r="K662" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
@@ -38661,16 +38661,16 @@
         </is>
       </c>
       <c r="C663" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D663" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E663" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F663" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G663" t="n">
         <v>0</v>
@@ -38685,13 +38685,13 @@
         <v>0</v>
       </c>
       <c r="K663" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
@@ -38700,13 +38700,13 @@
         </is>
       </c>
       <c r="C664" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D664" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E664" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F664" t="n">
         <v>0</v>
@@ -38721,16 +38721,16 @@
         <v>0</v>
       </c>
       <c r="J664" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K664" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
@@ -38745,7 +38745,7 @@
         <v>1</v>
       </c>
       <c r="E665" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F665" t="n">
         <v>0</v>
@@ -38763,13 +38763,13 @@
         <v>1</v>
       </c>
       <c r="K665" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
@@ -38799,16 +38799,16 @@
         <v>0</v>
       </c>
       <c r="J666" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K666" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
@@ -38838,16 +38838,16 @@
         <v>0</v>
       </c>
       <c r="J667" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K667" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B668" t="inlineStr">
@@ -38856,10 +38856,10 @@
         </is>
       </c>
       <c r="C668" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D668" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E668" t="n">
         <v>0</v>
@@ -38868,7 +38868,7 @@
         <v>0</v>
       </c>
       <c r="G668" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H668" t="n">
         <v>0</v>
@@ -38880,45 +38880,84 @@
         <v>1</v>
       </c>
       <c r="K668" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>GUTSHIFT</t>
+        </is>
+      </c>
+      <c r="C669" t="n">
+        <v>1</v>
+      </c>
+      <c r="D669" t="n">
+        <v>0</v>
+      </c>
+      <c r="E669" t="n">
+        <v>0</v>
+      </c>
+      <c r="F669" t="n">
+        <v>0</v>
+      </c>
+      <c r="G669" t="n">
+        <v>1</v>
+      </c>
+      <c r="H669" t="n">
+        <v>0</v>
+      </c>
+      <c r="I669" t="n">
+        <v>0</v>
+      </c>
+      <c r="J669" t="n">
+        <v>1</v>
+      </c>
+      <c r="K669" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="B669" t="inlineStr">
+      <c r="B670" t="inlineStr">
         <is>
           <t>GUTSHIFT</t>
         </is>
       </c>
-      <c r="C669" t="n">
-        <v>0</v>
-      </c>
-      <c r="D669" t="n">
-        <v>1</v>
-      </c>
-      <c r="E669" t="n">
-        <v>0</v>
-      </c>
-      <c r="F669" t="n">
-        <v>0</v>
-      </c>
-      <c r="G669" t="n">
-        <v>0</v>
-      </c>
-      <c r="H669" t="n">
-        <v>0</v>
-      </c>
-      <c r="I669" t="n">
-        <v>0</v>
-      </c>
-      <c r="J669" t="n">
-        <v>0</v>
-      </c>
-      <c r="K669" t="n">
+      <c r="C670" t="n">
+        <v>0</v>
+      </c>
+      <c r="D670" t="n">
+        <v>1</v>
+      </c>
+      <c r="E670" t="n">
+        <v>0</v>
+      </c>
+      <c r="F670" t="n">
+        <v>0</v>
+      </c>
+      <c r="G670" t="n">
+        <v>0</v>
+      </c>
+      <c r="H670" t="n">
+        <v>0</v>
+      </c>
+      <c r="I670" t="n">
+        <v>0</v>
+      </c>
+      <c r="J670" t="n">
+        <v>0</v>
+      </c>
+      <c r="K670" t="n">
         <v>1</v>
       </c>
     </row>

--- a/daily_ethnicity_mix.xlsx
+++ b/daily_ethnicity_mix.xlsx
@@ -10367,16 +10367,16 @@
         <v>4</v>
       </c>
       <c r="K216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L216" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M216" t="n">
         <v>20</v>
       </c>
       <c r="N216" t="n">
-        <v>80</v>
+        <v>76.90000000000001</v>
       </c>
     </row>
     <row r="217">
@@ -10392,7 +10392,7 @@
         <v>6</v>
       </c>
       <c r="D217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E217" t="n">
         <v>2</v>
@@ -10413,16 +10413,16 @@
         <v>5</v>
       </c>
       <c r="K217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L217" t="n">
         <v>23</v>
       </c>
       <c r="M217" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N217" t="n">
-        <v>65.2</v>
+        <v>60.9</v>
       </c>
     </row>
     <row r="218">
@@ -10484,7 +10484,7 @@
         <v>12</v>
       </c>
       <c r="D219" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E219" t="n">
         <v>2</v>
@@ -10505,16 +10505,16 @@
         <v>4</v>
       </c>
       <c r="K219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L219" t="n">
         <v>47</v>
       </c>
       <c r="M219" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N219" t="n">
-        <v>78.7</v>
+        <v>76.59999999999999</v>
       </c>
     </row>
     <row r="220">
@@ -10821,10 +10821,10 @@
         <v>0</v>
       </c>
       <c r="I226" t="n">
+        <v>10</v>
+      </c>
+      <c r="J226" t="n">
         <v>11</v>
-      </c>
-      <c r="J226" t="n">
-        <v>10</v>
       </c>
       <c r="K226" t="n">
         <v>0</v>
@@ -10849,7 +10849,7 @@
         <v>53</v>
       </c>
       <c r="C227" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D227" t="n">
         <v>34</v>
@@ -10870,7 +10870,7 @@
         <v>13</v>
       </c>
       <c r="J227" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K227" t="n">
         <v>0</v>
@@ -10879,10 +10879,10 @@
         <v>187</v>
       </c>
       <c r="M227" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N227" t="n">
-        <v>80.2</v>
+        <v>79.7</v>
       </c>
     </row>
     <row r="228">
@@ -10892,7 +10892,7 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C228" t="n">
         <v>19</v>
@@ -10922,13 +10922,13 @@
         <v>0</v>
       </c>
       <c r="L228" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M228" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N228" t="n">
-        <v>76.09999999999999</v>
+        <v>75.90000000000001</v>
       </c>
     </row>
     <row r="229">
@@ -10944,7 +10944,7 @@
         <v>33</v>
       </c>
       <c r="D229" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E229" t="n">
         <v>0</v>
@@ -10959,22 +10959,22 @@
         <v>1</v>
       </c>
       <c r="I229" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J229" t="n">
         <v>14</v>
       </c>
       <c r="K229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L229" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="M229" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N229" t="n">
-        <v>74.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
     </row>
     <row r="230">
@@ -11051,10 +11051,10 @@
         <v>1</v>
       </c>
       <c r="I231" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J231" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K231" t="n">
         <v>0</v>
@@ -11143,7 +11143,7 @@
         <v>1</v>
       </c>
       <c r="I233" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J233" t="n">
         <v>5</v>
@@ -11152,13 +11152,13 @@
         <v>0</v>
       </c>
       <c r="L233" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M233" t="n">
         <v>61</v>
       </c>
       <c r="N233" t="n">
-        <v>84.7</v>
+        <v>85.90000000000001</v>
       </c>
     </row>
     <row r="234">
@@ -11214,7 +11214,7 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C235" t="n">
         <v>12</v>
@@ -11241,16 +11241,16 @@
         <v>3</v>
       </c>
       <c r="K235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L235" t="n">
         <v>39</v>
       </c>
       <c r="M235" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N235" t="n">
-        <v>82.09999999999999</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="236">
@@ -11312,7 +11312,7 @@
         <v>54</v>
       </c>
       <c r="D237" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E237" t="n">
         <v>5</v>
@@ -11330,19 +11330,19 @@
         <v>19</v>
       </c>
       <c r="J237" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K237" t="n">
         <v>0</v>
       </c>
       <c r="L237" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="M237" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="N237" t="n">
-        <v>72.2</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="238">
@@ -11358,7 +11358,7 @@
         <v>16</v>
       </c>
       <c r="D238" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E238" t="n">
         <v>0</v>
@@ -11382,13 +11382,13 @@
         <v>0</v>
       </c>
       <c r="L238" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M238" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N238" t="n">
-        <v>79.5</v>
+        <v>79.09999999999999</v>
       </c>
     </row>
     <row r="239">
@@ -11490,7 +11490,7 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C241" t="n">
         <v>11</v>
@@ -11520,13 +11520,13 @@
         <v>0</v>
       </c>
       <c r="L241" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M241" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N241" t="n">
-        <v>74.40000000000001</v>
+        <v>73.7</v>
       </c>
     </row>
     <row r="242">
@@ -12413,7 +12413,7 @@
         <v>14</v>
       </c>
       <c r="C261" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D261" t="n">
         <v>13</v>
@@ -12434,7 +12434,7 @@
         <v>4</v>
       </c>
       <c r="J261" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K261" t="n">
         <v>0</v>
@@ -12443,10 +12443,10 @@
         <v>64</v>
       </c>
       <c r="M261" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N261" t="n">
-        <v>84.40000000000001</v>
+        <v>82.8</v>
       </c>
     </row>
     <row r="262">
@@ -12456,13 +12456,13 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C262" t="n">
         <v>16</v>
       </c>
       <c r="D262" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E262" t="n">
         <v>0</v>
@@ -12483,16 +12483,16 @@
         <v>7</v>
       </c>
       <c r="K262" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L262" t="n">
         <v>49</v>
       </c>
       <c r="M262" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N262" t="n">
-        <v>79.59999999999999</v>
+        <v>75.5</v>
       </c>
     </row>
     <row r="263">
@@ -12594,7 +12594,7 @@
         </is>
       </c>
       <c r="B265" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C265" t="n">
         <v>42</v>
@@ -12621,16 +12621,16 @@
         <v>29</v>
       </c>
       <c r="K265" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L265" t="n">
         <v>228</v>
       </c>
       <c r="M265" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="N265" t="n">
-        <v>78.09999999999999</v>
+        <v>77.2</v>
       </c>
     </row>
     <row r="266">
@@ -12640,7 +12640,7 @@
         </is>
       </c>
       <c r="B266" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C266" t="n">
         <v>41</v>
@@ -12661,22 +12661,22 @@
         <v>5</v>
       </c>
       <c r="I266" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J266" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K266" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L266" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M266" t="n">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="N266" t="n">
-        <v>81.5</v>
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="267">
@@ -12710,10 +12710,10 @@
         <v>8</v>
       </c>
       <c r="J267" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K267" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L267" t="n">
         <v>85</v>
@@ -12891,13 +12891,13 @@
         <v>0</v>
       </c>
       <c r="I271" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J271" t="n">
         <v>16</v>
       </c>
       <c r="K271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L271" t="n">
         <v>141</v>
@@ -12919,13 +12919,13 @@
         <v>47</v>
       </c>
       <c r="C272" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D272" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E272" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F272" t="n">
         <v>6</v>
@@ -12937,22 +12937,22 @@
         <v>1</v>
       </c>
       <c r="I272" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J272" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K272" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L272" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M272" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N272" t="n">
-        <v>78.09999999999999</v>
+        <v>76.90000000000001</v>
       </c>
     </row>
     <row r="273">
@@ -12962,7 +12962,7 @@
         </is>
       </c>
       <c r="B273" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C273" t="n">
         <v>32</v>
@@ -12989,16 +12989,16 @@
         <v>17</v>
       </c>
       <c r="K273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L273" t="n">
         <v>97</v>
       </c>
       <c r="M273" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N273" t="n">
-        <v>73.2</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="274">
@@ -13008,7 +13008,7 @@
         </is>
       </c>
       <c r="B274" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C274" t="n">
         <v>16</v>
@@ -13020,7 +13020,7 @@
         <v>1</v>
       </c>
       <c r="F274" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G274" t="n">
         <v>0</v>
@@ -13032,19 +13032,19 @@
         <v>13</v>
       </c>
       <c r="J274" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K274" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L274" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M274" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="N274" t="n">
-        <v>75.5</v>
+        <v>72.8</v>
       </c>
     </row>
     <row r="275">
@@ -13078,10 +13078,10 @@
         <v>7</v>
       </c>
       <c r="J275" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L275" t="n">
         <v>94</v>
@@ -13121,13 +13121,13 @@
         <v>0</v>
       </c>
       <c r="I276" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J276" t="n">
         <v>16</v>
       </c>
       <c r="K276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L276" t="n">
         <v>117</v>
@@ -13146,10 +13146,10 @@
         </is>
       </c>
       <c r="B277" t="n">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C277" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D277" t="n">
         <v>19</v>
@@ -13170,19 +13170,19 @@
         <v>19</v>
       </c>
       <c r="J277" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K277" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L277" t="n">
         <v>292</v>
       </c>
       <c r="M277" t="n">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="N277" t="n">
-        <v>84.90000000000001</v>
+        <v>83.59999999999999</v>
       </c>
     </row>
     <row r="278">
@@ -13290,10 +13290,10 @@
         <v>30</v>
       </c>
       <c r="D280" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E280" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F280" t="n">
         <v>1</v>
@@ -13308,10 +13308,10 @@
         <v>15</v>
       </c>
       <c r="J280" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K280" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L280" t="n">
         <v>100</v>
@@ -13339,7 +13339,7 @@
         <v>8</v>
       </c>
       <c r="E281" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F281" t="n">
         <v>14</v>
@@ -13357,16 +13357,16 @@
         <v>19</v>
       </c>
       <c r="K281" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L281" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M281" t="n">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="N281" t="n">
-        <v>90.09999999999999</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="282">
@@ -13382,7 +13382,7 @@
         <v>23</v>
       </c>
       <c r="D282" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E282" t="n">
         <v>7</v>
@@ -13397,22 +13397,22 @@
         <v>3</v>
       </c>
       <c r="I282" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J282" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K282" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L282" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="M282" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N282" t="n">
-        <v>81.09999999999999</v>
+        <v>80.59999999999999</v>
       </c>
     </row>
     <row r="283">
@@ -13560,13 +13560,13 @@
         </is>
       </c>
       <c r="B286" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C286" t="n">
         <v>43</v>
       </c>
       <c r="D286" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E286" t="n">
         <v>4</v>
@@ -13581,22 +13581,22 @@
         <v>1</v>
       </c>
       <c r="I286" t="n">
+        <v>16</v>
+      </c>
+      <c r="J286" t="n">
         <v>17</v>
       </c>
-      <c r="J286" t="n">
-        <v>15</v>
-      </c>
       <c r="K286" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L286" t="n">
         <v>136</v>
       </c>
       <c r="M286" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="N286" t="n">
-        <v>76.5</v>
+        <v>74.3</v>
       </c>
     </row>
     <row r="287">
@@ -13612,7 +13612,7 @@
         <v>30</v>
       </c>
       <c r="D287" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E287" t="n">
         <v>3</v>
@@ -13627,10 +13627,10 @@
         <v>0</v>
       </c>
       <c r="I287" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J287" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K287" t="n">
         <v>0</v>
@@ -13639,10 +13639,10 @@
         <v>122</v>
       </c>
       <c r="M287" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N287" t="n">
-        <v>75.40000000000001</v>
+        <v>74.59999999999999</v>
       </c>
     </row>
     <row r="288">
@@ -13652,7 +13652,7 @@
         </is>
       </c>
       <c r="B288" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C288" t="n">
         <v>19</v>
@@ -13679,16 +13679,16 @@
         <v>12</v>
       </c>
       <c r="K288" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L288" t="n">
         <v>46</v>
       </c>
       <c r="M288" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N288" t="n">
-        <v>65.2</v>
+        <v>63</v>
       </c>
     </row>
     <row r="289">
@@ -13707,7 +13707,7 @@
         <v>1</v>
       </c>
       <c r="E289" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F289" t="n">
         <v>1</v>
@@ -13725,16 +13725,16 @@
         <v>4</v>
       </c>
       <c r="K289" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L289" t="n">
         <v>20</v>
       </c>
       <c r="M289" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N289" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="290">
@@ -14710,7 +14710,7 @@
         </is>
       </c>
       <c r="B311" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C311" t="n">
         <v>7</v>
@@ -14737,16 +14737,16 @@
         <v>0</v>
       </c>
       <c r="K311" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L311" t="n">
         <v>30</v>
       </c>
       <c r="M311" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N311" t="n">
-        <v>40</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="312">
@@ -14851,7 +14851,7 @@
         <v>0</v>
       </c>
       <c r="C314" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D314" t="n">
         <v>0</v>
@@ -14875,16 +14875,16 @@
         <v>0</v>
       </c>
       <c r="K314" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L314" t="n">
         <v>13</v>
       </c>
       <c r="M314" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N314" t="n">
-        <v>46.2</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="315">
@@ -15170,19 +15170,19 @@
         </is>
       </c>
       <c r="B321" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C321" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D321" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E321" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F321" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G321" t="n">
         <v>0</v>
@@ -15191,22 +15191,22 @@
         <v>0</v>
       </c>
       <c r="I321" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J321" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K321" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="L321" t="n">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="M321" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="N321" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -15220,7 +15220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M722"/>
+  <dimension ref="A1:M726"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24824,10 +24824,10 @@
         <v>4</v>
       </c>
       <c r="L213" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M213" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="214">
@@ -24848,7 +24848,7 @@
         <v>6</v>
       </c>
       <c r="E214" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F214" t="n">
         <v>2</v>
@@ -24869,7 +24869,7 @@
         <v>5</v>
       </c>
       <c r="L214" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M214" t="n">
         <v>23</v>
@@ -24938,7 +24938,7 @@
         <v>10</v>
       </c>
       <c r="E216" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F216" t="n">
         <v>2</v>
@@ -24959,7 +24959,7 @@
         <v>4</v>
       </c>
       <c r="L216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M216" t="n">
         <v>39</v>
@@ -26780,7 +26780,7 @@
         <v>13</v>
       </c>
       <c r="D257" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E257" t="n">
         <v>12</v>
@@ -26801,7 +26801,7 @@
         <v>3</v>
       </c>
       <c r="K257" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L257" t="n">
         <v>0</v>
@@ -26822,7 +26822,7 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D258" t="n">
         <v>15</v>
@@ -26849,7 +26849,7 @@
         <v>7</v>
       </c>
       <c r="L258" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M258" t="n">
         <v>45</v>
@@ -26912,7 +26912,7 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D260" t="n">
         <v>18</v>
@@ -26939,7 +26939,7 @@
         <v>24</v>
       </c>
       <c r="L260" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M260" t="n">
         <v>181</v>
@@ -26957,7 +26957,7 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D261" t="n">
         <v>33</v>
@@ -26978,16 +26978,16 @@
         <v>5</v>
       </c>
       <c r="J261" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K261" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L261" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M261" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="262">
@@ -27026,10 +27026,10 @@
         <v>7</v>
       </c>
       <c r="K262" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M262" t="n">
         <v>61</v>
@@ -27158,13 +27158,13 @@
         <v>0</v>
       </c>
       <c r="J265" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K265" t="n">
         <v>11</v>
       </c>
       <c r="L265" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M265" t="n">
         <v>128</v>
@@ -27185,13 +27185,13 @@
         <v>46</v>
       </c>
       <c r="D266" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E266" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F266" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G266" t="n">
         <v>6</v>
@@ -27203,16 +27203,16 @@
         <v>1</v>
       </c>
       <c r="J266" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K266" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L266" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M266" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="267">
@@ -27227,7 +27227,7 @@
         </is>
       </c>
       <c r="C267" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D267" t="n">
         <v>17</v>
@@ -27254,7 +27254,7 @@
         <v>4</v>
       </c>
       <c r="L267" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M267" t="n">
         <v>61</v>
@@ -27272,7 +27272,7 @@
         </is>
       </c>
       <c r="C268" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D268" t="n">
         <v>13</v>
@@ -27284,7 +27284,7 @@
         <v>1</v>
       </c>
       <c r="G268" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -27296,13 +27296,13 @@
         <v>10</v>
       </c>
       <c r="K268" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L268" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M268" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="269">
@@ -27341,10 +27341,10 @@
         <v>4</v>
       </c>
       <c r="K269" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M269" t="n">
         <v>66</v>
@@ -27386,10 +27386,10 @@
         <v>8</v>
       </c>
       <c r="K270" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M270" t="n">
         <v>83</v>
@@ -27407,10 +27407,10 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D271" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E271" t="n">
         <v>17</v>
@@ -27431,10 +27431,10 @@
         <v>17</v>
       </c>
       <c r="K271" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L271" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M271" t="n">
         <v>268</v>
@@ -27548,10 +27548,10 @@
         <v>18</v>
       </c>
       <c r="E274" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F274" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G274" t="n">
         <v>1</v>
@@ -27566,10 +27566,10 @@
         <v>13</v>
       </c>
       <c r="K274" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M274" t="n">
         <v>78</v>
@@ -27596,7 +27596,7 @@
         <v>8</v>
       </c>
       <c r="F275" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G275" t="n">
         <v>14</v>
@@ -27614,10 +27614,10 @@
         <v>15</v>
       </c>
       <c r="L275" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M275" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="276">
@@ -27638,7 +27638,7 @@
         <v>13</v>
       </c>
       <c r="E276" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F276" t="n">
         <v>7</v>
@@ -27653,16 +27653,16 @@
         <v>2</v>
       </c>
       <c r="J276" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K276" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M276" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="277">
@@ -27812,13 +27812,13 @@
         </is>
       </c>
       <c r="C280" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D280" t="n">
         <v>20</v>
       </c>
       <c r="E280" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F280" t="n">
         <v>2</v>
@@ -27836,10 +27836,10 @@
         <v>10</v>
       </c>
       <c r="K280" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L280" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M280" t="n">
         <v>90</v>
@@ -27863,7 +27863,7 @@
         <v>17</v>
       </c>
       <c r="E281" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F281" t="n">
         <v>1</v>
@@ -27878,10 +27878,10 @@
         <v>0</v>
       </c>
       <c r="J281" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K281" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L281" t="n">
         <v>0</v>
@@ -27902,7 +27902,7 @@
         </is>
       </c>
       <c r="C282" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D282" t="n">
         <v>4</v>
@@ -27929,7 +27929,7 @@
         <v>5</v>
       </c>
       <c r="L282" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M282" t="n">
         <v>19</v>
@@ -28892,7 +28892,7 @@
         </is>
       </c>
       <c r="C304" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D304" t="n">
         <v>2</v>
@@ -28919,7 +28919,7 @@
         <v>0</v>
       </c>
       <c r="L304" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M304" t="n">
         <v>18</v>
@@ -29342,10 +29342,10 @@
         </is>
       </c>
       <c r="C314" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D314" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E314" t="n">
         <v>0</v>
@@ -29354,7 +29354,7 @@
         <v>0</v>
       </c>
       <c r="G314" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -29363,16 +29363,16 @@
         <v>0</v>
       </c>
       <c r="J314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K314" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L314" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M314" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="315">
@@ -32063,10 +32063,10 @@
         <v>0</v>
       </c>
       <c r="J374" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K374" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L374" t="n">
         <v>0</v>
@@ -32090,7 +32090,7 @@
         <v>49</v>
       </c>
       <c r="D375" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E375" t="n">
         <v>32</v>
@@ -32111,7 +32111,7 @@
         <v>11</v>
       </c>
       <c r="K375" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L375" t="n">
         <v>0</v>
@@ -32132,7 +32132,7 @@
         </is>
       </c>
       <c r="C376" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D376" t="n">
         <v>13</v>
@@ -32156,7 +32156,7 @@
         <v>6</v>
       </c>
       <c r="K376" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L376" t="n">
         <v>0</v>
@@ -32183,7 +32183,7 @@
         <v>13</v>
       </c>
       <c r="E377" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F377" t="n">
         <v>0</v>
@@ -32204,7 +32204,7 @@
         <v>7</v>
       </c>
       <c r="L377" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M377" t="n">
         <v>66</v>
@@ -32288,10 +32288,10 @@
         <v>0</v>
       </c>
       <c r="J379" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K379" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L379" t="n">
         <v>0</v>
@@ -32498,7 +32498,7 @@
         <v>32</v>
       </c>
       <c r="E384" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F384" t="n">
         <v>2</v>
@@ -32516,7 +32516,7 @@
         <v>14</v>
       </c>
       <c r="K384" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L384" t="n">
         <v>0</v>
@@ -34157,19 +34157,19 @@
         </is>
       </c>
       <c r="C421" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D421" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E421" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F421" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G421" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H421" t="n">
         <v>0</v>
@@ -34178,16 +34178,16 @@
         <v>0</v>
       </c>
       <c r="J421" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K421" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L421" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="M421" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="422">
@@ -35336,7 +35336,7 @@
         <v>1</v>
       </c>
       <c r="F447" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G447" t="n">
         <v>1</v>
@@ -35354,7 +35354,7 @@
         <v>3</v>
       </c>
       <c r="L447" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M447" t="n">
         <v>17</v>
@@ -38138,10 +38138,10 @@
         <v>0</v>
       </c>
       <c r="J509" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K509" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L509" t="n">
         <v>0</v>
@@ -38273,10 +38273,10 @@
         <v>0</v>
       </c>
       <c r="J512" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K512" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L512" t="n">
         <v>0</v>
@@ -38342,7 +38342,7 @@
         </is>
       </c>
       <c r="C514" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D514" t="n">
         <v>0</v>
@@ -38369,7 +38369,7 @@
         <v>0</v>
       </c>
       <c r="L514" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M514" t="n">
         <v>4</v>
@@ -38483,7 +38483,7 @@
         <v>1</v>
       </c>
       <c r="E517" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F517" t="n">
         <v>0</v>
@@ -38501,7 +38501,7 @@
         <v>0</v>
       </c>
       <c r="K517" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L517" t="n">
         <v>0</v>
@@ -38612,7 +38612,7 @@
         </is>
       </c>
       <c r="C520" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D520" t="n">
         <v>0</v>
@@ -38636,7 +38636,7 @@
         <v>1</v>
       </c>
       <c r="K520" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L520" t="n">
         <v>0</v>
@@ -39293,7 +39293,7 @@
         <v>1</v>
       </c>
       <c r="E535" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F535" t="n">
         <v>0</v>
@@ -39314,7 +39314,7 @@
         <v>0</v>
       </c>
       <c r="L535" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M535" t="n">
         <v>4</v>
@@ -39623,10 +39623,10 @@
         <v>0</v>
       </c>
       <c r="J542" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K542" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L542" t="n">
         <v>0</v>
@@ -39923,7 +39923,7 @@
         <v>3</v>
       </c>
       <c r="E549" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F549" t="n">
         <v>1</v>
@@ -39938,13 +39938,13 @@
         <v>0</v>
       </c>
       <c r="J549" t="n">
+        <v>3</v>
+      </c>
+      <c r="K549" t="n">
         <v>4</v>
       </c>
-      <c r="K549" t="n">
-        <v>3</v>
-      </c>
       <c r="L549" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M549" t="n">
         <v>13</v>
@@ -40007,7 +40007,7 @@
         </is>
       </c>
       <c r="C551" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D551" t="n">
         <v>0</v>
@@ -40034,7 +40034,7 @@
         <v>0</v>
       </c>
       <c r="L551" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M551" t="n">
         <v>2</v>
@@ -41132,7 +41132,7 @@
         </is>
       </c>
       <c r="C576" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D576" t="n">
         <v>1</v>
@@ -41159,7 +41159,7 @@
         <v>0</v>
       </c>
       <c r="L576" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M576" t="n">
         <v>4</v>
@@ -41270,7 +41270,7 @@
         <v>0</v>
       </c>
       <c r="D579" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E579" t="n">
         <v>0</v>
@@ -41294,7 +41294,7 @@
         <v>0</v>
       </c>
       <c r="L579" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M579" t="n">
         <v>3</v>
@@ -41573,19 +41573,19 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="C586" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D586" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E586" t="n">
         <v>0</v>
@@ -41594,7 +41594,7 @@
         <v>0</v>
       </c>
       <c r="G586" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H586" t="n">
         <v>0</v>
@@ -41603,22 +41603,22 @@
         <v>0</v>
       </c>
       <c r="J586" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K586" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L586" t="n">
         <v>0</v>
       </c>
       <c r="M586" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
@@ -41627,7 +41627,7 @@
         </is>
       </c>
       <c r="C587" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D587" t="n">
         <v>0</v>
@@ -41639,7 +41639,7 @@
         <v>0</v>
       </c>
       <c r="G587" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H587" t="n">
         <v>0</v>
@@ -41657,13 +41657,13 @@
         <v>0</v>
       </c>
       <c r="M587" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
@@ -41672,7 +41672,7 @@
         </is>
       </c>
       <c r="C588" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D588" t="n">
         <v>0</v>
@@ -41702,13 +41702,13 @@
         <v>0</v>
       </c>
       <c r="M588" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
@@ -41717,7 +41717,7 @@
         </is>
       </c>
       <c r="C589" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D589" t="n">
         <v>0</v>
@@ -41729,7 +41729,7 @@
         <v>0</v>
       </c>
       <c r="G589" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H589" t="n">
         <v>0</v>
@@ -41738,7 +41738,7 @@
         <v>0</v>
       </c>
       <c r="J589" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K589" t="n">
         <v>0</v>
@@ -41747,13 +41747,13 @@
         <v>0</v>
       </c>
       <c r="M589" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
@@ -41762,7 +41762,7 @@
         </is>
       </c>
       <c r="C590" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D590" t="n">
         <v>0</v>
@@ -41774,7 +41774,7 @@
         <v>0</v>
       </c>
       <c r="G590" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H590" t="n">
         <v>0</v>
@@ -41783,7 +41783,7 @@
         <v>0</v>
       </c>
       <c r="J590" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K590" t="n">
         <v>0</v>
@@ -41792,13 +41792,13 @@
         <v>0</v>
       </c>
       <c r="M590" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
@@ -41807,7 +41807,7 @@
         </is>
       </c>
       <c r="C591" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D591" t="n">
         <v>0</v>
@@ -41828,7 +41828,7 @@
         <v>0</v>
       </c>
       <c r="J591" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K591" t="n">
         <v>0</v>
@@ -41843,7 +41843,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
@@ -41852,7 +41852,7 @@
         </is>
       </c>
       <c r="C592" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D592" t="n">
         <v>0</v>
@@ -41873,7 +41873,7 @@
         <v>0</v>
       </c>
       <c r="J592" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K592" t="n">
         <v>0</v>
@@ -41882,13 +41882,13 @@
         <v>0</v>
       </c>
       <c r="M592" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
@@ -41897,7 +41897,7 @@
         </is>
       </c>
       <c r="C593" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D593" t="n">
         <v>0</v>
@@ -41918,7 +41918,7 @@
         <v>0</v>
       </c>
       <c r="J593" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K593" t="n">
         <v>0</v>
@@ -41927,13 +41927,13 @@
         <v>0</v>
       </c>
       <c r="M593" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
@@ -41942,10 +41942,10 @@
         </is>
       </c>
       <c r="C594" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D594" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E594" t="n">
         <v>0</v>
@@ -41972,13 +41972,13 @@
         <v>0</v>
       </c>
       <c r="M594" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
@@ -41987,13 +41987,13 @@
         </is>
       </c>
       <c r="C595" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D595" t="n">
         <v>2</v>
       </c>
       <c r="E595" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F595" t="n">
         <v>0</v>
@@ -42008,7 +42008,7 @@
         <v>0</v>
       </c>
       <c r="J595" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K595" t="n">
         <v>0</v>
@@ -42017,13 +42017,13 @@
         <v>0</v>
       </c>
       <c r="M595" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
@@ -42032,13 +42032,13 @@
         </is>
       </c>
       <c r="C596" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D596" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E596" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F596" t="n">
         <v>0</v>
@@ -42062,13 +42062,13 @@
         <v>0</v>
       </c>
       <c r="M596" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
@@ -42098,7 +42098,7 @@
         <v>0</v>
       </c>
       <c r="J597" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K597" t="n">
         <v>0</v>
@@ -42107,13 +42107,13 @@
         <v>0</v>
       </c>
       <c r="M597" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
@@ -42122,13 +42122,13 @@
         </is>
       </c>
       <c r="C598" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D598" t="n">
         <v>0</v>
       </c>
       <c r="E598" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F598" t="n">
         <v>0</v>
@@ -42143,7 +42143,7 @@
         <v>0</v>
       </c>
       <c r="J598" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K598" t="n">
         <v>0</v>
@@ -42152,13 +42152,13 @@
         <v>0</v>
       </c>
       <c r="M598" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
@@ -42173,7 +42173,7 @@
         <v>0</v>
       </c>
       <c r="E599" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F599" t="n">
         <v>0</v>
@@ -42188,22 +42188,22 @@
         <v>0</v>
       </c>
       <c r="J599" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K599" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L599" t="n">
         <v>0</v>
       </c>
       <c r="M599" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
@@ -42212,7 +42212,7 @@
         </is>
       </c>
       <c r="C600" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D600" t="n">
         <v>0</v>
@@ -42236,19 +42236,19 @@
         <v>0</v>
       </c>
       <c r="K600" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L600" t="n">
         <v>0</v>
       </c>
       <c r="M600" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
@@ -42257,10 +42257,10 @@
         </is>
       </c>
       <c r="C601" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D601" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E601" t="n">
         <v>0</v>
@@ -42287,13 +42287,13 @@
         <v>0</v>
       </c>
       <c r="M601" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
@@ -42305,7 +42305,7 @@
         <v>0</v>
       </c>
       <c r="D602" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E602" t="n">
         <v>0</v>
@@ -42332,13 +42332,13 @@
         <v>0</v>
       </c>
       <c r="M602" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
@@ -42347,13 +42347,13 @@
         </is>
       </c>
       <c r="C603" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D603" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E603" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F603" t="n">
         <v>0</v>
@@ -42371,19 +42371,19 @@
         <v>0</v>
       </c>
       <c r="K603" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L603" t="n">
         <v>0</v>
       </c>
       <c r="M603" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
@@ -42392,19 +42392,19 @@
         </is>
       </c>
       <c r="C604" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D604" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E604" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F604" t="n">
         <v>0</v>
       </c>
       <c r="G604" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H604" t="n">
         <v>0</v>
@@ -42416,19 +42416,19 @@
         <v>0</v>
       </c>
       <c r="K604" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L604" t="n">
         <v>0</v>
       </c>
       <c r="M604" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
@@ -42437,19 +42437,19 @@
         </is>
       </c>
       <c r="C605" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D605" t="n">
         <v>1</v>
       </c>
       <c r="E605" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F605" t="n">
         <v>0</v>
       </c>
       <c r="G605" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H605" t="n">
         <v>0</v>
@@ -42461,19 +42461,19 @@
         <v>0</v>
       </c>
       <c r="K605" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L605" t="n">
         <v>0</v>
       </c>
       <c r="M605" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
@@ -42485,10 +42485,10 @@
         <v>0</v>
       </c>
       <c r="D606" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E606" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F606" t="n">
         <v>0</v>
@@ -42506,19 +42506,19 @@
         <v>0</v>
       </c>
       <c r="K606" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L606" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M606" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
@@ -42533,13 +42533,13 @@
         <v>0</v>
       </c>
       <c r="E607" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F607" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G607" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H607" t="n">
         <v>0</v>
@@ -42551,19 +42551,19 @@
         <v>0</v>
       </c>
       <c r="K607" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L607" t="n">
         <v>0</v>
       </c>
       <c r="M607" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
@@ -42572,19 +42572,19 @@
         </is>
       </c>
       <c r="C608" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D608" t="n">
         <v>0</v>
       </c>
       <c r="E608" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F608" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G608" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H608" t="n">
         <v>0</v>
@@ -42593,7 +42593,7 @@
         <v>0</v>
       </c>
       <c r="J608" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K608" t="n">
         <v>0</v>
@@ -42602,13 +42602,13 @@
         <v>0</v>
       </c>
       <c r="M608" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
@@ -42617,16 +42617,16 @@
         </is>
       </c>
       <c r="C609" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D609" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E609" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F609" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G609" t="n">
         <v>0</v>
@@ -42638,22 +42638,22 @@
         <v>0</v>
       </c>
       <c r="J609" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K609" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L609" t="n">
         <v>0</v>
       </c>
       <c r="M609" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
@@ -42662,16 +42662,16 @@
         </is>
       </c>
       <c r="C610" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D610" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E610" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F610" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G610" t="n">
         <v>0</v>
@@ -42683,22 +42683,22 @@
         <v>0</v>
       </c>
       <c r="J610" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K610" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L610" t="n">
         <v>0</v>
       </c>
       <c r="M610" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
@@ -42707,7 +42707,7 @@
         </is>
       </c>
       <c r="C611" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D611" t="n">
         <v>1</v>
@@ -42728,7 +42728,7 @@
         <v>0</v>
       </c>
       <c r="J611" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K611" t="n">
         <v>0</v>
@@ -42743,7 +42743,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
@@ -42752,22 +42752,22 @@
         </is>
       </c>
       <c r="C612" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D612" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E612" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F612" t="n">
         <v>0</v>
       </c>
       <c r="G612" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H612" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I612" t="n">
         <v>0</v>
@@ -42782,13 +42782,13 @@
         <v>0</v>
       </c>
       <c r="M612" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
@@ -42797,10 +42797,10 @@
         </is>
       </c>
       <c r="C613" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D613" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E613" t="n">
         <v>2</v>
@@ -42809,31 +42809,31 @@
         <v>0</v>
       </c>
       <c r="G613" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H613" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I613" t="n">
         <v>0</v>
       </c>
       <c r="J613" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K613" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L613" t="n">
         <v>0</v>
       </c>
       <c r="M613" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
@@ -42842,13 +42842,13 @@
         </is>
       </c>
       <c r="C614" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D614" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E614" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F614" t="n">
         <v>0</v>
@@ -42863,22 +42863,22 @@
         <v>0</v>
       </c>
       <c r="J614" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K614" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L614" t="n">
         <v>0</v>
       </c>
       <c r="M614" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
@@ -42887,22 +42887,22 @@
         </is>
       </c>
       <c r="C615" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D615" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E615" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F615" t="n">
         <v>0</v>
       </c>
       <c r="G615" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H615" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I615" t="n">
         <v>0</v>
@@ -42911,19 +42911,19 @@
         <v>1</v>
       </c>
       <c r="K615" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L615" t="n">
         <v>0</v>
       </c>
       <c r="M615" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
@@ -42932,19 +42932,19 @@
         </is>
       </c>
       <c r="C616" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D616" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E616" t="n">
         <v>2</v>
       </c>
       <c r="F616" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G616" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H616" t="n">
         <v>1</v>
@@ -42956,7 +42956,7 @@
         <v>1</v>
       </c>
       <c r="K616" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L616" t="n">
         <v>0</v>
@@ -42968,7 +42968,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
@@ -42977,43 +42977,43 @@
         </is>
       </c>
       <c r="C617" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D617" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E617" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F617" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G617" t="n">
         <v>0</v>
       </c>
       <c r="H617" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I617" t="n">
         <v>0</v>
       </c>
       <c r="J617" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K617" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L617" t="n">
         <v>0</v>
       </c>
       <c r="M617" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
@@ -43022,19 +43022,19 @@
         </is>
       </c>
       <c r="C618" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D618" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E618" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F618" t="n">
         <v>0</v>
       </c>
       <c r="G618" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H618" t="n">
         <v>0</v>
@@ -43043,7 +43043,7 @@
         <v>0</v>
       </c>
       <c r="J618" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K618" t="n">
         <v>1</v>
@@ -43052,13 +43052,13 @@
         <v>0</v>
       </c>
       <c r="M618" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
@@ -43067,19 +43067,19 @@
         </is>
       </c>
       <c r="C619" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D619" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E619" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F619" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G619" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H619" t="n">
         <v>0</v>
@@ -43097,13 +43097,13 @@
         <v>0</v>
       </c>
       <c r="M619" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
@@ -43112,16 +43112,16 @@
         </is>
       </c>
       <c r="C620" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D620" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E620" t="n">
         <v>1</v>
       </c>
       <c r="F620" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G620" t="n">
         <v>0</v>
@@ -43133,7 +43133,7 @@
         <v>0</v>
       </c>
       <c r="J620" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K620" t="n">
         <v>1</v>
@@ -43142,13 +43142,13 @@
         <v>0</v>
       </c>
       <c r="M620" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
@@ -43157,10 +43157,10 @@
         </is>
       </c>
       <c r="C621" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D621" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E621" t="n">
         <v>1</v>
@@ -43178,22 +43178,22 @@
         <v>0</v>
       </c>
       <c r="J621" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K621" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L621" t="n">
         <v>0</v>
       </c>
       <c r="M621" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
@@ -43202,13 +43202,13 @@
         </is>
       </c>
       <c r="C622" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D622" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E622" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F622" t="n">
         <v>0</v>
@@ -43223,22 +43223,22 @@
         <v>0</v>
       </c>
       <c r="J622" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K622" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L622" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M622" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
@@ -43247,10 +43247,10 @@
         </is>
       </c>
       <c r="C623" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D623" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E623" t="n">
         <v>0</v>
@@ -43268,7 +43268,7 @@
         <v>0</v>
       </c>
       <c r="J623" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K623" t="n">
         <v>0</v>
@@ -43277,13 +43277,13 @@
         <v>1</v>
       </c>
       <c r="M623" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
@@ -43292,10 +43292,10 @@
         </is>
       </c>
       <c r="C624" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D624" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E624" t="n">
         <v>0</v>
@@ -43319,16 +43319,16 @@
         <v>0</v>
       </c>
       <c r="L624" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M624" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
@@ -43373,7 +43373,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
@@ -43385,7 +43385,7 @@
         <v>0</v>
       </c>
       <c r="D626" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E626" t="n">
         <v>0</v>
@@ -43412,13 +43412,13 @@
         <v>0</v>
       </c>
       <c r="M626" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
@@ -43427,10 +43427,10 @@
         </is>
       </c>
       <c r="C627" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D627" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E627" t="n">
         <v>0</v>
@@ -43439,7 +43439,7 @@
         <v>0</v>
       </c>
       <c r="G627" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H627" t="n">
         <v>0</v>
@@ -43463,7 +43463,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
@@ -43472,7 +43472,7 @@
         </is>
       </c>
       <c r="C628" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D628" t="n">
         <v>0</v>
@@ -43481,10 +43481,10 @@
         <v>0</v>
       </c>
       <c r="F628" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G628" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H628" t="n">
         <v>0</v>
@@ -43502,13 +43502,13 @@
         <v>0</v>
       </c>
       <c r="M628" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
@@ -43526,10 +43526,10 @@
         <v>0</v>
       </c>
       <c r="F629" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G629" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H629" t="n">
         <v>0</v>
@@ -43553,7 +43553,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
@@ -43565,7 +43565,7 @@
         <v>0</v>
       </c>
       <c r="D630" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E630" t="n">
         <v>0</v>
@@ -43574,7 +43574,7 @@
         <v>0</v>
       </c>
       <c r="G630" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H630" t="n">
         <v>0</v>
@@ -43598,7 +43598,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
@@ -43610,7 +43610,7 @@
         <v>0</v>
       </c>
       <c r="D631" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E631" t="n">
         <v>0</v>
@@ -43634,7 +43634,7 @@
         <v>0</v>
       </c>
       <c r="L631" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M631" t="n">
         <v>1</v>
@@ -43643,16 +43643,16 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="C632" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D632" t="n">
         <v>0</v>
@@ -43664,7 +43664,7 @@
         <v>0</v>
       </c>
       <c r="G632" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H632" t="n">
         <v>0</v>
@@ -43679,25 +43679,25 @@
         <v>0</v>
       </c>
       <c r="L632" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M632" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="C633" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D633" t="n">
         <v>0</v>
@@ -43718,13 +43718,13 @@
         <v>0</v>
       </c>
       <c r="J633" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K633" t="n">
         <v>0</v>
       </c>
       <c r="L633" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M633" t="n">
         <v>2</v>
@@ -43733,7 +43733,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
@@ -43742,7 +43742,7 @@
         </is>
       </c>
       <c r="C634" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D634" t="n">
         <v>0</v>
@@ -43754,7 +43754,7 @@
         <v>0</v>
       </c>
       <c r="G634" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H634" t="n">
         <v>0</v>
@@ -43772,13 +43772,13 @@
         <v>0</v>
       </c>
       <c r="M634" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
@@ -43787,7 +43787,7 @@
         </is>
       </c>
       <c r="C635" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D635" t="n">
         <v>0</v>
@@ -43808,22 +43808,22 @@
         <v>0</v>
       </c>
       <c r="J635" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K635" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L635" t="n">
         <v>0</v>
       </c>
       <c r="M635" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
@@ -43832,10 +43832,10 @@
         </is>
       </c>
       <c r="C636" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D636" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E636" t="n">
         <v>0</v>
@@ -43853,7 +43853,7 @@
         <v>0</v>
       </c>
       <c r="J636" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K636" t="n">
         <v>0</v>
@@ -43862,13 +43862,13 @@
         <v>0</v>
       </c>
       <c r="M636" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
@@ -43877,7 +43877,7 @@
         </is>
       </c>
       <c r="C637" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D637" t="n">
         <v>0</v>
@@ -43901,7 +43901,7 @@
         <v>0</v>
       </c>
       <c r="K637" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L637" t="n">
         <v>0</v>
@@ -43913,7 +43913,7 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
@@ -43922,10 +43922,10 @@
         </is>
       </c>
       <c r="C638" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D638" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E638" t="n">
         <v>0</v>
@@ -43943,22 +43943,22 @@
         <v>0</v>
       </c>
       <c r="J638" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K638" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L638" t="n">
         <v>0</v>
       </c>
       <c r="M638" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
@@ -43967,16 +43967,16 @@
         </is>
       </c>
       <c r="C639" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D639" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E639" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F639" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G639" t="n">
         <v>0</v>
@@ -43988,7 +43988,7 @@
         <v>0</v>
       </c>
       <c r="J639" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K639" t="n">
         <v>0</v>
@@ -43997,13 +43997,13 @@
         <v>0</v>
       </c>
       <c r="M639" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
@@ -44012,13 +44012,13 @@
         </is>
       </c>
       <c r="C640" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D640" t="n">
         <v>0</v>
       </c>
       <c r="E640" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F640" t="n">
         <v>0</v>
@@ -44036,19 +44036,19 @@
         <v>0</v>
       </c>
       <c r="K640" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L640" t="n">
         <v>0</v>
       </c>
       <c r="M640" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
@@ -44057,16 +44057,16 @@
         </is>
       </c>
       <c r="C641" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D641" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E641" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F641" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G641" t="n">
         <v>0</v>
@@ -44078,7 +44078,7 @@
         <v>0</v>
       </c>
       <c r="J641" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K641" t="n">
         <v>0</v>
@@ -44087,13 +44087,13 @@
         <v>0</v>
       </c>
       <c r="M641" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
@@ -44102,13 +44102,13 @@
         </is>
       </c>
       <c r="C642" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D642" t="n">
         <v>0</v>
       </c>
       <c r="E642" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F642" t="n">
         <v>0</v>
@@ -44138,7 +44138,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
@@ -44150,10 +44150,10 @@
         <v>1</v>
       </c>
       <c r="D643" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E643" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F643" t="n">
         <v>0</v>
@@ -44168,7 +44168,7 @@
         <v>0</v>
       </c>
       <c r="J643" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K643" t="n">
         <v>0</v>
@@ -44177,13 +44177,13 @@
         <v>0</v>
       </c>
       <c r="M643" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
@@ -44192,10 +44192,10 @@
         </is>
       </c>
       <c r="C644" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D644" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E644" t="n">
         <v>0</v>
@@ -44213,22 +44213,22 @@
         <v>0</v>
       </c>
       <c r="J644" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K644" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L644" t="n">
         <v>0</v>
       </c>
       <c r="M644" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
@@ -44240,10 +44240,10 @@
         <v>1</v>
       </c>
       <c r="D645" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E645" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F645" t="n">
         <v>0</v>
@@ -44258,7 +44258,7 @@
         <v>0</v>
       </c>
       <c r="J645" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K645" t="n">
         <v>0</v>
@@ -44267,13 +44267,13 @@
         <v>0</v>
       </c>
       <c r="M645" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
@@ -44282,10 +44282,10 @@
         </is>
       </c>
       <c r="C646" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D646" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E646" t="n">
         <v>0</v>
@@ -44303,22 +44303,22 @@
         <v>0</v>
       </c>
       <c r="J646" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K646" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L646" t="n">
         <v>0</v>
       </c>
       <c r="M646" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
@@ -44363,7 +44363,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
@@ -44372,13 +44372,13 @@
         </is>
       </c>
       <c r="C648" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D648" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E648" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F648" t="n">
         <v>0</v>
@@ -44396,19 +44396,19 @@
         <v>0</v>
       </c>
       <c r="K648" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L648" t="n">
         <v>0</v>
       </c>
       <c r="M648" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
@@ -44417,16 +44417,16 @@
         </is>
       </c>
       <c r="C649" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D649" t="n">
         <v>0</v>
       </c>
       <c r="E649" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F649" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G649" t="n">
         <v>0</v>
@@ -44441,19 +44441,19 @@
         <v>0</v>
       </c>
       <c r="K649" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L649" t="n">
         <v>0</v>
       </c>
       <c r="M649" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
@@ -44462,10 +44462,10 @@
         </is>
       </c>
       <c r="C650" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D650" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E650" t="n">
         <v>0</v>
@@ -44486,19 +44486,19 @@
         <v>0</v>
       </c>
       <c r="K650" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L650" t="n">
         <v>0</v>
       </c>
       <c r="M650" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
@@ -44507,16 +44507,16 @@
         </is>
       </c>
       <c r="C651" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D651" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E651" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F651" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G651" t="n">
         <v>0</v>
@@ -44531,19 +44531,19 @@
         <v>0</v>
       </c>
       <c r="K651" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L651" t="n">
         <v>0</v>
       </c>
       <c r="M651" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
@@ -44555,16 +44555,16 @@
         <v>0</v>
       </c>
       <c r="D652" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E652" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F652" t="n">
         <v>0</v>
       </c>
       <c r="G652" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H652" t="n">
         <v>0</v>
@@ -44579,7 +44579,7 @@
         <v>0</v>
       </c>
       <c r="L652" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M652" t="n">
         <v>2</v>
@@ -44588,7 +44588,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
@@ -44597,10 +44597,10 @@
         </is>
       </c>
       <c r="C653" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D653" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E653" t="n">
         <v>0</v>
@@ -44618,10 +44618,10 @@
         <v>0</v>
       </c>
       <c r="J653" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K653" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L653" t="n">
         <v>0</v>
@@ -44633,7 +44633,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
@@ -44642,19 +44642,19 @@
         </is>
       </c>
       <c r="C654" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D654" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E654" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F654" t="n">
         <v>0</v>
       </c>
       <c r="G654" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H654" t="n">
         <v>0</v>
@@ -44663,22 +44663,22 @@
         <v>0</v>
       </c>
       <c r="J654" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K654" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L654" t="n">
         <v>0</v>
       </c>
       <c r="M654" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
@@ -44687,10 +44687,10 @@
         </is>
       </c>
       <c r="C655" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D655" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E655" t="n">
         <v>0</v>
@@ -44708,7 +44708,7 @@
         <v>0</v>
       </c>
       <c r="J655" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K655" t="n">
         <v>0</v>
@@ -44717,13 +44717,13 @@
         <v>0</v>
       </c>
       <c r="M655" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
@@ -44732,13 +44732,13 @@
         </is>
       </c>
       <c r="C656" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D656" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E656" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F656" t="n">
         <v>0</v>
@@ -44753,22 +44753,22 @@
         <v>0</v>
       </c>
       <c r="J656" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K656" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L656" t="n">
         <v>0</v>
       </c>
       <c r="M656" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
@@ -44777,7 +44777,7 @@
         </is>
       </c>
       <c r="C657" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D657" t="n">
         <v>1</v>
@@ -44801,19 +44801,19 @@
         <v>0</v>
       </c>
       <c r="K657" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L657" t="n">
         <v>0</v>
       </c>
       <c r="M657" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
@@ -44822,43 +44822,43 @@
         </is>
       </c>
       <c r="C658" t="n">
+        <v>0</v>
+      </c>
+      <c r="D658" t="n">
+        <v>2</v>
+      </c>
+      <c r="E658" t="n">
+        <v>1</v>
+      </c>
+      <c r="F658" t="n">
+        <v>0</v>
+      </c>
+      <c r="G658" t="n">
+        <v>0</v>
+      </c>
+      <c r="H658" t="n">
+        <v>0</v>
+      </c>
+      <c r="I658" t="n">
+        <v>0</v>
+      </c>
+      <c r="J658" t="n">
+        <v>1</v>
+      </c>
+      <c r="K658" t="n">
+        <v>0</v>
+      </c>
+      <c r="L658" t="n">
+        <v>0</v>
+      </c>
+      <c r="M658" t="n">
         <v>4</v>
-      </c>
-      <c r="D658" t="n">
-        <v>6</v>
-      </c>
-      <c r="E658" t="n">
-        <v>3</v>
-      </c>
-      <c r="F658" t="n">
-        <v>0</v>
-      </c>
-      <c r="G658" t="n">
-        <v>1</v>
-      </c>
-      <c r="H658" t="n">
-        <v>0</v>
-      </c>
-      <c r="I658" t="n">
-        <v>0</v>
-      </c>
-      <c r="J658" t="n">
-        <v>1</v>
-      </c>
-      <c r="K658" t="n">
-        <v>0</v>
-      </c>
-      <c r="L658" t="n">
-        <v>0</v>
-      </c>
-      <c r="M658" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
@@ -44867,43 +44867,43 @@
         </is>
       </c>
       <c r="C659" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D659" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E659" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F659" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G659" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H659" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I659" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J659" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K659" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L659" t="n">
         <v>0</v>
       </c>
       <c r="M659" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
@@ -44912,19 +44912,19 @@
         </is>
       </c>
       <c r="C660" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D660" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E660" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F660" t="n">
         <v>0</v>
       </c>
       <c r="G660" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H660" t="n">
         <v>0</v>
@@ -44933,22 +44933,22 @@
         <v>0</v>
       </c>
       <c r="J660" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K660" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L660" t="n">
         <v>0</v>
       </c>
       <c r="M660" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
@@ -44957,43 +44957,43 @@
         </is>
       </c>
       <c r="C661" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D661" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E661" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F661" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G661" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H661" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I661" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J661" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K661" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L661" t="n">
         <v>0</v>
       </c>
       <c r="M661" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
@@ -45005,7 +45005,7 @@
         <v>0</v>
       </c>
       <c r="D662" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E662" t="n">
         <v>0</v>
@@ -45026,19 +45026,19 @@
         <v>0</v>
       </c>
       <c r="K662" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L662" t="n">
         <v>0</v>
       </c>
       <c r="M662" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
@@ -45050,7 +45050,7 @@
         <v>1</v>
       </c>
       <c r="D663" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E663" t="n">
         <v>0</v>
@@ -45068,22 +45068,22 @@
         <v>0</v>
       </c>
       <c r="J663" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K663" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L663" t="n">
         <v>0</v>
       </c>
       <c r="M663" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
@@ -45095,7 +45095,7 @@
         <v>0</v>
       </c>
       <c r="D664" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E664" t="n">
         <v>0</v>
@@ -45116,19 +45116,19 @@
         <v>0</v>
       </c>
       <c r="K664" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L664" t="n">
         <v>0</v>
       </c>
       <c r="M664" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
@@ -45137,13 +45137,13 @@
         </is>
       </c>
       <c r="C665" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D665" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E665" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F665" t="n">
         <v>0</v>
@@ -45164,16 +45164,16 @@
         <v>0</v>
       </c>
       <c r="L665" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M665" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
@@ -45185,7 +45185,7 @@
         <v>0</v>
       </c>
       <c r="D666" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E666" t="n">
         <v>0</v>
@@ -45206,19 +45206,19 @@
         <v>0</v>
       </c>
       <c r="K666" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L666" t="n">
         <v>0</v>
       </c>
       <c r="M666" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
@@ -45230,13 +45230,13 @@
         <v>0</v>
       </c>
       <c r="D667" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E667" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F667" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G667" t="n">
         <v>0</v>
@@ -45254,16 +45254,16 @@
         <v>0</v>
       </c>
       <c r="L667" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M667" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B668" t="inlineStr">
@@ -45275,7 +45275,7 @@
         <v>0</v>
       </c>
       <c r="D668" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E668" t="n">
         <v>0</v>
@@ -45284,7 +45284,7 @@
         <v>0</v>
       </c>
       <c r="G668" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H668" t="n">
         <v>0</v>
@@ -45308,7 +45308,7 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
@@ -45326,7 +45326,7 @@
         <v>0</v>
       </c>
       <c r="F669" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G669" t="n">
         <v>0</v>
@@ -45344,16 +45344,16 @@
         <v>0</v>
       </c>
       <c r="L669" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M669" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B670" t="inlineStr">
@@ -45374,7 +45374,7 @@
         <v>0</v>
       </c>
       <c r="G670" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H670" t="n">
         <v>0</v>
@@ -45389,7 +45389,7 @@
         <v>0</v>
       </c>
       <c r="L670" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M670" t="n">
         <v>1</v>
@@ -45398,12 +45398,12 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>Ashwagandha</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="C671" t="n">
@@ -45419,7 +45419,7 @@
         <v>0</v>
       </c>
       <c r="G671" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H671" t="n">
         <v>0</v>
@@ -45428,31 +45428,31 @@
         <v>0</v>
       </c>
       <c r="J671" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K671" t="n">
         <v>0</v>
       </c>
       <c r="L671" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M671" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>Ashwagandha</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="C672" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D672" t="n">
         <v>0</v>
@@ -45473,37 +45473,37 @@
         <v>0</v>
       </c>
       <c r="J672" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K672" t="n">
         <v>0</v>
       </c>
       <c r="L672" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M672" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>Ashwagandha</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="C673" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D673" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E673" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F673" t="n">
         <v>0</v>
@@ -45524,16 +45524,16 @@
         <v>0</v>
       </c>
       <c r="L673" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M673" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
@@ -45551,10 +45551,10 @@
         <v>0</v>
       </c>
       <c r="F674" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G674" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H674" t="n">
         <v>0</v>
@@ -45563,7 +45563,7 @@
         <v>0</v>
       </c>
       <c r="J674" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K674" t="n">
         <v>0</v>
@@ -45572,13 +45572,13 @@
         <v>0</v>
       </c>
       <c r="M674" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
@@ -45587,7 +45587,7 @@
         </is>
       </c>
       <c r="C675" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D675" t="n">
         <v>0</v>
@@ -45608,7 +45608,7 @@
         <v>0</v>
       </c>
       <c r="J675" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K675" t="n">
         <v>0</v>
@@ -45617,13 +45617,13 @@
         <v>0</v>
       </c>
       <c r="M675" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
@@ -45632,10 +45632,10 @@
         </is>
       </c>
       <c r="C676" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D676" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E676" t="n">
         <v>0</v>
@@ -45656,19 +45656,19 @@
         <v>0</v>
       </c>
       <c r="K676" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L676" t="n">
         <v>0</v>
       </c>
       <c r="M676" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
@@ -45677,16 +45677,16 @@
         </is>
       </c>
       <c r="C677" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D677" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E677" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F677" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G677" t="n">
         <v>0</v>
@@ -45698,22 +45698,22 @@
         <v>0</v>
       </c>
       <c r="J677" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K677" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L677" t="n">
         <v>0</v>
       </c>
       <c r="M677" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B678" t="inlineStr">
@@ -45722,7 +45722,7 @@
         </is>
       </c>
       <c r="C678" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D678" t="n">
         <v>0</v>
@@ -45740,7 +45740,7 @@
         <v>0</v>
       </c>
       <c r="I678" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J678" t="n">
         <v>0</v>
@@ -45758,7 +45758,7 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
@@ -45767,10 +45767,10 @@
         </is>
       </c>
       <c r="C679" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D679" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E679" t="n">
         <v>0</v>
@@ -45788,22 +45788,22 @@
         <v>0</v>
       </c>
       <c r="J679" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K679" t="n">
+        <v>1</v>
+      </c>
+      <c r="L679" t="n">
+        <v>0</v>
+      </c>
+      <c r="M679" t="n">
         <v>4</v>
-      </c>
-      <c r="L679" t="n">
-        <v>0</v>
-      </c>
-      <c r="M679" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
@@ -45812,13 +45812,13 @@
         </is>
       </c>
       <c r="C680" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D680" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E680" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F680" t="n">
         <v>0</v>
@@ -45833,22 +45833,22 @@
         <v>0</v>
       </c>
       <c r="J680" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K680" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L680" t="n">
         <v>0</v>
       </c>
       <c r="M680" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
@@ -45875,7 +45875,7 @@
         <v>0</v>
       </c>
       <c r="I681" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J681" t="n">
         <v>0</v>
@@ -45887,13 +45887,13 @@
         <v>0</v>
       </c>
       <c r="M681" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
@@ -45902,7 +45902,7 @@
         </is>
       </c>
       <c r="C682" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D682" t="n">
         <v>0</v>
@@ -45926,19 +45926,19 @@
         <v>1</v>
       </c>
       <c r="K682" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L682" t="n">
         <v>0</v>
       </c>
       <c r="M682" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
@@ -45947,13 +45947,13 @@
         </is>
       </c>
       <c r="C683" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D683" t="n">
         <v>0</v>
       </c>
       <c r="E683" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F683" t="n">
         <v>0</v>
@@ -45968,7 +45968,7 @@
         <v>0</v>
       </c>
       <c r="J683" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K683" t="n">
         <v>0</v>
@@ -45977,13 +45977,13 @@
         <v>0</v>
       </c>
       <c r="M683" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
@@ -45992,7 +45992,7 @@
         </is>
       </c>
       <c r="C684" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D684" t="n">
         <v>0</v>
@@ -46016,19 +46016,19 @@
         <v>0</v>
       </c>
       <c r="K684" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L684" t="n">
         <v>0</v>
       </c>
       <c r="M684" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
@@ -46040,7 +46040,7 @@
         <v>0</v>
       </c>
       <c r="D685" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E685" t="n">
         <v>0</v>
@@ -46058,22 +46058,22 @@
         <v>0</v>
       </c>
       <c r="J685" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K685" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L685" t="n">
         <v>0</v>
       </c>
       <c r="M685" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
@@ -46082,13 +46082,13 @@
         </is>
       </c>
       <c r="C686" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D686" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E686" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F686" t="n">
         <v>0</v>
@@ -46112,13 +46112,13 @@
         <v>0</v>
       </c>
       <c r="M686" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
@@ -46130,13 +46130,13 @@
         <v>0</v>
       </c>
       <c r="D687" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E687" t="n">
         <v>0</v>
       </c>
       <c r="F687" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G687" t="n">
         <v>0</v>
@@ -46151,19 +46151,19 @@
         <v>0</v>
       </c>
       <c r="K687" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L687" t="n">
         <v>0</v>
       </c>
       <c r="M687" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
@@ -46172,10 +46172,10 @@
         </is>
       </c>
       <c r="C688" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D688" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E688" t="n">
         <v>0</v>
@@ -46190,7 +46190,7 @@
         <v>0</v>
       </c>
       <c r="I688" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J688" t="n">
         <v>0</v>
@@ -46202,13 +46202,13 @@
         <v>0</v>
       </c>
       <c r="M688" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
@@ -46217,10 +46217,10 @@
         </is>
       </c>
       <c r="C689" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D689" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E689" t="n">
         <v>0</v>
@@ -46241,19 +46241,19 @@
         <v>0</v>
       </c>
       <c r="K689" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L689" t="n">
         <v>0</v>
       </c>
       <c r="M689" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
@@ -46262,16 +46262,16 @@
         </is>
       </c>
       <c r="C690" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D690" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E690" t="n">
         <v>0</v>
       </c>
       <c r="F690" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G690" t="n">
         <v>0</v>
@@ -46286,7 +46286,7 @@
         <v>0</v>
       </c>
       <c r="K690" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L690" t="n">
         <v>0</v>
@@ -46298,7 +46298,7 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
@@ -46307,7 +46307,7 @@
         </is>
       </c>
       <c r="C691" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D691" t="n">
         <v>0</v>
@@ -46325,25 +46325,25 @@
         <v>0</v>
       </c>
       <c r="I691" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J691" t="n">
         <v>0</v>
       </c>
       <c r="K691" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L691" t="n">
         <v>0</v>
       </c>
       <c r="M691" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
@@ -46352,7 +46352,7 @@
         </is>
       </c>
       <c r="C692" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D692" t="n">
         <v>0</v>
@@ -46373,22 +46373,22 @@
         <v>0</v>
       </c>
       <c r="J692" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K692" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L692" t="n">
         <v>0</v>
       </c>
       <c r="M692" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
@@ -46421,19 +46421,19 @@
         <v>0</v>
       </c>
       <c r="K693" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L693" t="n">
         <v>0</v>
       </c>
       <c r="M693" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
@@ -46442,7 +46442,7 @@
         </is>
       </c>
       <c r="C694" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D694" t="n">
         <v>0</v>
@@ -46466,19 +46466,19 @@
         <v>0</v>
       </c>
       <c r="K694" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L694" t="n">
         <v>0</v>
       </c>
       <c r="M694" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
@@ -46487,10 +46487,10 @@
         </is>
       </c>
       <c r="C695" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D695" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E695" t="n">
         <v>0</v>
@@ -46508,22 +46508,22 @@
         <v>0</v>
       </c>
       <c r="J695" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K695" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L695" t="n">
         <v>0</v>
       </c>
       <c r="M695" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
@@ -46568,7 +46568,7 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
@@ -46598,7 +46598,7 @@
         <v>0</v>
       </c>
       <c r="J697" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K697" t="n">
         <v>0</v>
@@ -46607,13 +46607,13 @@
         <v>0</v>
       </c>
       <c r="M697" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
@@ -46625,7 +46625,7 @@
         <v>1</v>
       </c>
       <c r="D698" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E698" t="n">
         <v>0</v>
@@ -46652,13 +46652,13 @@
         <v>0</v>
       </c>
       <c r="M698" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
@@ -46703,7 +46703,7 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
@@ -46733,7 +46733,7 @@
         <v>0</v>
       </c>
       <c r="J700" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K700" t="n">
         <v>0</v>
@@ -46742,13 +46742,13 @@
         <v>0</v>
       </c>
       <c r="M700" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
@@ -46781,19 +46781,19 @@
         <v>0</v>
       </c>
       <c r="K701" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L701" t="n">
         <v>0</v>
       </c>
       <c r="M701" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
@@ -46838,7 +46838,7 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
@@ -46847,7 +46847,7 @@
         </is>
       </c>
       <c r="C703" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D703" t="n">
         <v>0</v>
@@ -46856,7 +46856,7 @@
         <v>0</v>
       </c>
       <c r="F703" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G703" t="n">
         <v>0</v>
@@ -46877,13 +46877,13 @@
         <v>0</v>
       </c>
       <c r="M703" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
@@ -46913,7 +46913,7 @@
         <v>0</v>
       </c>
       <c r="J704" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K704" t="n">
         <v>0</v>
@@ -46922,13 +46922,13 @@
         <v>0</v>
       </c>
       <c r="M704" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
@@ -46937,7 +46937,7 @@
         </is>
       </c>
       <c r="C705" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D705" t="n">
         <v>0</v>
@@ -46967,13 +46967,13 @@
         <v>0</v>
       </c>
       <c r="M705" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
@@ -46991,7 +46991,7 @@
         <v>0</v>
       </c>
       <c r="F706" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G706" t="n">
         <v>0</v>
@@ -47006,7 +47006,7 @@
         <v>0</v>
       </c>
       <c r="K706" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L706" t="n">
         <v>0</v>
@@ -47018,7 +47018,7 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
@@ -47027,7 +47027,7 @@
         </is>
       </c>
       <c r="C707" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D707" t="n">
         <v>0</v>
@@ -47048,22 +47048,22 @@
         <v>0</v>
       </c>
       <c r="J707" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K707" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L707" t="n">
         <v>0</v>
       </c>
       <c r="M707" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
@@ -47072,7 +47072,7 @@
         </is>
       </c>
       <c r="C708" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D708" t="n">
         <v>0</v>
@@ -47102,22 +47102,22 @@
         <v>0</v>
       </c>
       <c r="M708" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>GUTSHIFT</t>
+          <t>Ashwagandha</t>
         </is>
       </c>
       <c r="C709" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D709" t="n">
         <v>0</v>
@@ -47138,34 +47138,34 @@
         <v>0</v>
       </c>
       <c r="J709" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K709" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L709" t="n">
         <v>0</v>
       </c>
       <c r="M709" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>GUTSHIFT</t>
+          <t>Ashwagandha</t>
         </is>
       </c>
       <c r="C710" t="n">
         <v>0</v>
       </c>
       <c r="D710" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E710" t="n">
         <v>0</v>
@@ -47174,7 +47174,7 @@
         <v>0</v>
       </c>
       <c r="G710" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H710" t="n">
         <v>0</v>
@@ -47186,34 +47186,34 @@
         <v>0</v>
       </c>
       <c r="K710" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L710" t="n">
         <v>0</v>
       </c>
       <c r="M710" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>GUTSHIFT</t>
+          <t>Ashwagandha</t>
         </is>
       </c>
       <c r="C711" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D711" t="n">
         <v>0</v>
       </c>
       <c r="E711" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F711" t="n">
         <v>0</v>
@@ -47243,7 +47243,7 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
@@ -47252,10 +47252,10 @@
         </is>
       </c>
       <c r="C712" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D712" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E712" t="n">
         <v>0</v>
@@ -47273,7 +47273,7 @@
         <v>0</v>
       </c>
       <c r="J712" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K712" t="n">
         <v>0</v>
@@ -47282,13 +47282,13 @@
         <v>0</v>
       </c>
       <c r="M712" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
@@ -47300,7 +47300,7 @@
         <v>0</v>
       </c>
       <c r="D713" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E713" t="n">
         <v>0</v>
@@ -47327,13 +47327,13 @@
         <v>0</v>
       </c>
       <c r="M713" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
@@ -47342,13 +47342,13 @@
         </is>
       </c>
       <c r="C714" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D714" t="n">
         <v>0</v>
       </c>
       <c r="E714" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F714" t="n">
         <v>0</v>
@@ -47378,7 +47378,7 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
@@ -47387,16 +47387,16 @@
         </is>
       </c>
       <c r="C715" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D715" t="n">
         <v>1</v>
       </c>
       <c r="E715" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F715" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G715" t="n">
         <v>0</v>
@@ -47417,13 +47417,13 @@
         <v>0</v>
       </c>
       <c r="M715" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
@@ -47432,7 +47432,7 @@
         </is>
       </c>
       <c r="C716" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D716" t="n">
         <v>0</v>
@@ -47444,7 +47444,7 @@
         <v>0</v>
       </c>
       <c r="G716" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H716" t="n">
         <v>0</v>
@@ -47468,7 +47468,7 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
@@ -47480,10 +47480,10 @@
         <v>1</v>
       </c>
       <c r="D717" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E717" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F717" t="n">
         <v>0</v>
@@ -47507,13 +47507,13 @@
         <v>0</v>
       </c>
       <c r="M717" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
@@ -47522,16 +47522,16 @@
         </is>
       </c>
       <c r="C718" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D718" t="n">
         <v>1</v>
       </c>
       <c r="E718" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F718" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G718" t="n">
         <v>0</v>
@@ -47546,19 +47546,19 @@
         <v>0</v>
       </c>
       <c r="K718" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L718" t="n">
         <v>0</v>
       </c>
       <c r="M718" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
@@ -47567,10 +47567,10 @@
         </is>
       </c>
       <c r="C719" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D719" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E719" t="n">
         <v>0</v>
@@ -47588,7 +47588,7 @@
         <v>0</v>
       </c>
       <c r="J719" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K719" t="n">
         <v>0</v>
@@ -47597,13 +47597,13 @@
         <v>0</v>
       </c>
       <c r="M719" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
@@ -47612,13 +47612,13 @@
         </is>
       </c>
       <c r="C720" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D720" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E720" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F720" t="n">
         <v>0</v>
@@ -47642,13 +47642,13 @@
         <v>0</v>
       </c>
       <c r="M720" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
@@ -47657,10 +47657,10 @@
         </is>
       </c>
       <c r="C721" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D721" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E721" t="n">
         <v>0</v>
@@ -47669,7 +47669,7 @@
         <v>0</v>
       </c>
       <c r="G721" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H721" t="n">
         <v>0</v>
@@ -47687,52 +47687,232 @@
         <v>0</v>
       </c>
       <c r="M721" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>GUTSHIFT</t>
+        </is>
+      </c>
+      <c r="C722" t="n">
+        <v>0</v>
+      </c>
+      <c r="D722" t="n">
+        <v>1</v>
+      </c>
+      <c r="E722" t="n">
+        <v>0</v>
+      </c>
+      <c r="F722" t="n">
+        <v>0</v>
+      </c>
+      <c r="G722" t="n">
+        <v>0</v>
+      </c>
+      <c r="H722" t="n">
+        <v>0</v>
+      </c>
+      <c r="I722" t="n">
+        <v>0</v>
+      </c>
+      <c r="J722" t="n">
+        <v>2</v>
+      </c>
+      <c r="K722" t="n">
+        <v>0</v>
+      </c>
+      <c r="L722" t="n">
+        <v>0</v>
+      </c>
+      <c r="M722" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>GUTSHIFT</t>
+        </is>
+      </c>
+      <c r="C723" t="n">
+        <v>0</v>
+      </c>
+      <c r="D723" t="n">
+        <v>2</v>
+      </c>
+      <c r="E723" t="n">
+        <v>0</v>
+      </c>
+      <c r="F723" t="n">
+        <v>0</v>
+      </c>
+      <c r="G723" t="n">
+        <v>0</v>
+      </c>
+      <c r="H723" t="n">
+        <v>0</v>
+      </c>
+      <c r="I723" t="n">
+        <v>0</v>
+      </c>
+      <c r="J723" t="n">
+        <v>0</v>
+      </c>
+      <c r="K723" t="n">
+        <v>0</v>
+      </c>
+      <c r="L723" t="n">
+        <v>0</v>
+      </c>
+      <c r="M723" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>GUTSHIFT</t>
+        </is>
+      </c>
+      <c r="C724" t="n">
+        <v>1</v>
+      </c>
+      <c r="D724" t="n">
+        <v>0</v>
+      </c>
+      <c r="E724" t="n">
+        <v>0</v>
+      </c>
+      <c r="F724" t="n">
+        <v>0</v>
+      </c>
+      <c r="G724" t="n">
+        <v>1</v>
+      </c>
+      <c r="H724" t="n">
+        <v>0</v>
+      </c>
+      <c r="I724" t="n">
+        <v>0</v>
+      </c>
+      <c r="J724" t="n">
+        <v>0</v>
+      </c>
+      <c r="K724" t="n">
+        <v>1</v>
+      </c>
+      <c r="L724" t="n">
+        <v>0</v>
+      </c>
+      <c r="M724" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="B722" t="inlineStr">
+      <c r="B725" t="inlineStr">
         <is>
           <t>GUTSHIFT</t>
         </is>
       </c>
-      <c r="C722" t="n">
-        <v>0</v>
-      </c>
-      <c r="D722" t="n">
-        <v>1</v>
-      </c>
-      <c r="E722" t="n">
-        <v>0</v>
-      </c>
-      <c r="F722" t="n">
-        <v>0</v>
-      </c>
-      <c r="G722" t="n">
-        <v>0</v>
-      </c>
-      <c r="H722" t="n">
-        <v>0</v>
-      </c>
-      <c r="I722" t="n">
-        <v>0</v>
-      </c>
-      <c r="J722" t="n">
-        <v>0</v>
-      </c>
-      <c r="K722" t="n">
-        <v>0</v>
-      </c>
-      <c r="L722" t="n">
-        <v>0</v>
-      </c>
-      <c r="M722" t="n">
-        <v>1</v>
+      <c r="C725" t="n">
+        <v>0</v>
+      </c>
+      <c r="D725" t="n">
+        <v>1</v>
+      </c>
+      <c r="E725" t="n">
+        <v>0</v>
+      </c>
+      <c r="F725" t="n">
+        <v>0</v>
+      </c>
+      <c r="G725" t="n">
+        <v>0</v>
+      </c>
+      <c r="H725" t="n">
+        <v>0</v>
+      </c>
+      <c r="I725" t="n">
+        <v>0</v>
+      </c>
+      <c r="J725" t="n">
+        <v>0</v>
+      </c>
+      <c r="K725" t="n">
+        <v>0</v>
+      </c>
+      <c r="L725" t="n">
+        <v>0</v>
+      </c>
+      <c r="M725" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C726" t="n">
+        <v>0</v>
+      </c>
+      <c r="D726" t="n">
+        <v>0</v>
+      </c>
+      <c r="E726" t="n">
+        <v>0</v>
+      </c>
+      <c r="F726" t="n">
+        <v>0</v>
+      </c>
+      <c r="G726" t="n">
+        <v>0</v>
+      </c>
+      <c r="H726" t="n">
+        <v>0</v>
+      </c>
+      <c r="I726" t="n">
+        <v>0</v>
+      </c>
+      <c r="J726" t="n">
+        <v>1</v>
+      </c>
+      <c r="K726" t="n">
+        <v>0</v>
+      </c>
+      <c r="L726" t="n">
+        <v>2</v>
+      </c>
+      <c r="M726" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/daily_ethnicity_mix.xlsx
+++ b/daily_ethnicity_mix.xlsx
@@ -15657,16 +15657,16 @@
         <v>1</v>
       </c>
       <c r="K331" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L331" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M331" t="n">
         <v>29</v>
       </c>
       <c r="N331" t="n">
-        <v>24</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="332">
@@ -35549,10 +35549,10 @@
         <v>0</v>
       </c>
       <c r="L436" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M436" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="437">
